--- a/pages/WR_progressions/Medals_Women_F200.xlsx
+++ b/pages/WR_progressions/Medals_Women_F200.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F658759-4F71-47FB-9720-7426953126F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC67BC5E-73A9-4B2C-93DF-63CFC7EB1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="9">
   <si>
     <t>8th</t>
   </si>
@@ -101,9 +101,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1400477D-CA59-426F-9BF4-08585135C868}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -470,71 +473,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10.234</v>
-      </c>
-      <c r="D2" s="1">
-        <v>10.308999999999999</v>
-      </c>
-      <c r="E2" s="1">
-        <v>10.397</v>
-      </c>
-      <c r="F2" s="1">
-        <v>10.612</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10.834</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10.029</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10.067</v>
+      </c>
+      <c r="E2" s="2">
+        <v>10.108000000000001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>10.263</v>
+      </c>
+      <c r="G2" s="2">
+        <v>10.56</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>10.356999999999999</v>
+        <v>10.234</v>
       </c>
       <c r="D3" s="1">
-        <v>10.401</v>
+        <v>10.308999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>10.416</v>
+        <v>10.397</v>
       </c>
       <c r="F3" s="1">
-        <v>10.558999999999999</v>
+        <v>10.612</v>
       </c>
       <c r="G3" s="1">
-        <v>10.734</v>
+        <v>10.834</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>10.489052051920808</v>
+        <v>10.356999999999999</v>
       </c>
       <c r="D4" s="1">
-        <v>10.518934081346424</v>
+        <v>10.401</v>
       </c>
       <c r="E4" s="1">
-        <v>10.520009935564939</v>
+        <v>10.416</v>
       </c>
       <c r="F4" s="1">
-        <v>10.753972995578923</v>
+        <v>10.558999999999999</v>
       </c>
       <c r="G4" s="1">
-        <v>10.952069484796398</v>
+        <v>10.734</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -542,137 +545,137 @@
         <v>2021</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>10.310016467387413</v>
+        <v>10.489052051920808</v>
       </c>
       <c r="D5" s="1">
-        <v>10.346016783538339</v>
+        <v>10.518934081346424</v>
       </c>
       <c r="E5" s="1">
-        <v>10.381071845668066</v>
+        <v>10.520009935564939</v>
       </c>
       <c r="F5" s="1">
-        <v>10.49501486793773</v>
+        <v>10.753972995578923</v>
       </c>
       <c r="G5" s="1">
-        <v>10.706001308511272</v>
+        <v>10.952069484796398</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
-        <v>10.364036792330612</v>
+        <v>10.310016467387413</v>
       </c>
       <c r="D6" s="1">
-        <v>10.461010940473942</v>
+        <v>10.346016783538339</v>
       </c>
       <c r="E6" s="1">
-        <v>10.478061558611657</v>
+        <v>10.381071845668066</v>
       </c>
       <c r="F6" s="1">
-        <v>10.512944062376802</v>
+        <v>10.49501486793773</v>
       </c>
       <c r="G6" s="1">
-        <v>10.634055562940317</v>
+        <v>10.706001308511272</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
-        <v>10.546051089758611</v>
+        <v>10.364036792330612</v>
       </c>
       <c r="D7" s="1">
-        <v>10.661928031985784</v>
+        <v>10.461010940473942</v>
       </c>
       <c r="E7" s="1">
-        <v>10.685029087023626</v>
+        <v>10.478061558611657</v>
       </c>
       <c r="F7" s="1">
-        <v>10.782962918588629</v>
+        <v>10.512944062376802</v>
       </c>
       <c r="G7" s="1">
-        <v>10.971930145378074</v>
+        <v>10.634055562940317</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1">
-        <v>10.645</v>
+        <v>10.546051089758611</v>
       </c>
       <c r="D8" s="1">
-        <v>10.712999999999999</v>
+        <v>10.661928031985784</v>
       </c>
       <c r="E8" s="1">
-        <v>10.81</v>
+        <v>10.685029087023626</v>
       </c>
       <c r="F8" s="1">
-        <v>10.975</v>
+        <v>10.782962918588629</v>
       </c>
       <c r="G8" s="1">
-        <v>11.101000000000001</v>
+        <v>10.971930145378074</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>10.724</v>
+        <v>10.645</v>
       </c>
       <c r="D9" s="1">
-        <v>10.763999999999999</v>
+        <v>10.712999999999999</v>
       </c>
       <c r="E9" s="1">
-        <v>10.816000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="F9" s="1">
-        <v>10.967000000000001</v>
+        <v>10.975</v>
       </c>
       <c r="G9" s="1">
-        <v>11.151</v>
+        <v>11.101000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>10.76</v>
+        <v>10.724</v>
       </c>
       <c r="D10" s="1">
-        <v>10.779</v>
+        <v>10.763999999999999</v>
       </c>
       <c r="E10" s="1">
-        <v>10.811999999999999</v>
+        <v>10.816000000000001</v>
       </c>
       <c r="F10" s="1">
-        <v>10.958</v>
+        <v>10.967000000000001</v>
       </c>
       <c r="G10" s="1">
-        <v>11.106999999999999</v>
+        <v>11.151</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -680,114 +683,114 @@
         <v>2016</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1">
-        <v>10.721</v>
+        <v>10.76</v>
       </c>
       <c r="D11" s="1">
-        <v>10.787000000000001</v>
+        <v>10.779</v>
       </c>
       <c r="E11" s="1">
-        <v>10.8</v>
+        <v>10.811999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>10.875</v>
+        <v>10.958</v>
       </c>
       <c r="G11" s="1">
-        <v>11.099</v>
+        <v>11.106999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>10.627000000000001</v>
+        <v>10.721</v>
       </c>
       <c r="D12" s="1">
-        <v>10.731999999999999</v>
+        <v>10.787000000000001</v>
       </c>
       <c r="E12" s="1">
-        <v>10.754</v>
+        <v>10.8</v>
       </c>
       <c r="F12" s="1">
-        <v>10.87</v>
+        <v>10.875</v>
       </c>
       <c r="G12" s="1">
-        <v>11.066000000000001</v>
+        <v>11.099</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>10.946</v>
+        <v>10.627000000000001</v>
       </c>
       <c r="D13" s="1">
-        <v>10.954000000000001</v>
+        <v>10.731999999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>10.962</v>
+        <v>10.754</v>
       </c>
       <c r="F13" s="1">
-        <v>11.047000000000001</v>
+        <v>10.87</v>
       </c>
       <c r="G13" s="1">
-        <v>11.218</v>
+        <v>11.066000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="1">
-        <v>10.957000000000001</v>
+        <v>10.946</v>
       </c>
       <c r="D14" s="1">
-        <v>11.057</v>
+        <v>10.954000000000001</v>
       </c>
       <c r="E14" s="1">
-        <v>11.07</v>
+        <v>10.962</v>
       </c>
       <c r="F14" s="1">
-        <v>11.208</v>
+        <v>11.047000000000001</v>
       </c>
       <c r="G14" s="1">
-        <v>11.452999999999999</v>
+        <v>11.218</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="1">
-        <v>10.782</v>
+        <v>10.957000000000001</v>
       </c>
       <c r="D15" s="1">
-        <v>11.004</v>
+        <v>11.057</v>
       </c>
       <c r="E15" s="1">
-        <v>11.032999999999999</v>
+        <v>11.07</v>
       </c>
       <c r="F15" s="1">
-        <v>11.09</v>
+        <v>11.208</v>
       </c>
       <c r="G15" s="1">
-        <v>11.228</v>
+        <v>11.452999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -795,114 +798,114 @@
         <v>2012</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>10.724</v>
+        <v>10.782</v>
       </c>
       <c r="D16" s="1">
-        <v>10.805</v>
+        <v>11.004</v>
       </c>
       <c r="E16" s="1">
-        <v>11.02</v>
+        <v>11.032999999999999</v>
       </c>
       <c r="F16" s="1">
-        <v>11.234</v>
+        <v>11.09</v>
       </c>
       <c r="G16" s="1">
-        <v>11.569000000000001</v>
+        <v>11.228</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1">
-        <v>11.12</v>
+        <v>10.724</v>
       </c>
       <c r="D17" s="1">
-        <v>11.12</v>
+        <v>10.805</v>
       </c>
       <c r="E17" s="1">
-        <v>11.151999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="F17" s="1">
-        <v>11.368</v>
+        <v>11.234</v>
       </c>
       <c r="G17" s="1">
-        <v>11.513999999999999</v>
+        <v>11.569000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="1">
-        <v>10.917999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="D18" s="1">
-        <v>11.03</v>
+        <v>11.12</v>
       </c>
       <c r="E18" s="1">
-        <v>11.077</v>
+        <v>11.151999999999999</v>
       </c>
       <c r="F18" s="1">
-        <v>11.202</v>
+        <v>11.368</v>
       </c>
       <c r="G18" s="1">
-        <v>11.442</v>
+        <v>11.513999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="1">
-        <v>10.971</v>
+        <v>10.917999999999999</v>
       </c>
       <c r="D19" s="1">
-        <v>11.134</v>
+        <v>11.03</v>
       </c>
       <c r="E19" s="1">
-        <v>11.148</v>
+        <v>11.077</v>
       </c>
       <c r="F19" s="1">
-        <v>11.430999999999999</v>
+        <v>11.202</v>
       </c>
       <c r="G19" s="1">
-        <v>11.613</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="1">
-        <v>10.904</v>
+        <v>10.971</v>
       </c>
       <c r="D20" s="1">
-        <v>11.002000000000001</v>
+        <v>11.134</v>
       </c>
       <c r="E20" s="1">
-        <v>11.093</v>
+        <v>11.148</v>
       </c>
       <c r="F20" s="1">
-        <v>11.28</v>
+        <v>11.430999999999999</v>
       </c>
       <c r="G20" s="1">
-        <v>11.417</v>
+        <v>11.613</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -910,110 +913,110 @@
         <v>2008</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1">
-        <v>10.962999999999999</v>
+        <v>10.904</v>
       </c>
       <c r="D21" s="1">
-        <v>11.106</v>
+        <v>11.002000000000001</v>
       </c>
       <c r="E21" s="1">
-        <v>11.14</v>
+        <v>11.093</v>
       </c>
       <c r="F21" s="1">
-        <v>11.4</v>
-      </c>
-      <c r="G21" s="1"/>
+        <v>11.28</v>
+      </c>
+      <c r="G21" s="1">
+        <v>11.417</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1">
-        <v>11.148999999999999</v>
+        <v>10.962999999999999</v>
       </c>
       <c r="D22" s="1">
-        <v>11.191000000000001</v>
+        <v>11.106</v>
       </c>
       <c r="E22" s="1">
-        <v>11.194000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F22" s="1">
-        <v>11.407999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="1">
-        <v>11.052</v>
+        <v>11.148999999999999</v>
       </c>
       <c r="D23" s="1">
-        <v>11.268000000000001</v>
+        <v>11.191000000000001</v>
       </c>
       <c r="E23" s="1">
-        <v>11.365</v>
+        <v>11.194000000000001</v>
       </c>
       <c r="F23" s="1">
-        <v>11.507</v>
-      </c>
-      <c r="G23" s="1">
-        <v>11.755000000000001</v>
-      </c>
+        <v>11.407999999999999</v>
+      </c>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="1">
-        <v>11.278</v>
+        <v>11.052</v>
       </c>
       <c r="D24" s="1">
-        <v>11.385999999999999</v>
+        <v>11.268000000000001</v>
       </c>
       <c r="E24" s="1">
-        <v>11.494</v>
+        <v>11.365</v>
       </c>
       <c r="F24" s="1">
-        <v>11.65</v>
+        <v>11.507</v>
       </c>
       <c r="G24" s="1">
-        <v>11.933</v>
+        <v>11.755000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1">
-        <v>11.339</v>
+        <v>11.278</v>
       </c>
       <c r="D25" s="1">
-        <v>11.45</v>
+        <v>11.385999999999999</v>
       </c>
       <c r="E25" s="1">
-        <v>11.452</v>
+        <v>11.494</v>
       </c>
       <c r="F25" s="1">
-        <v>11.558999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="G25" s="1">
-        <v>11.84</v>
+        <v>11.933</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -1021,132 +1024,155 @@
         <v>2004</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1">
-        <v>11.291</v>
+        <v>11.339</v>
       </c>
       <c r="D26" s="1">
-        <v>11.364000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="E26" s="1">
-        <v>11.364000000000001</v>
+        <v>11.452</v>
       </c>
       <c r="F26" s="1">
-        <v>11.597</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>11.558999999999999</v>
+      </c>
+      <c r="G26" s="1">
+        <v>11.84</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1">
-        <v>11.132999999999999</v>
+        <v>11.291</v>
       </c>
       <c r="D27" s="1">
-        <v>11.233000000000001</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="E27" s="1">
-        <v>11.285</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="F27" s="1">
-        <v>11.420999999999999</v>
-      </c>
-      <c r="G27" s="1">
-        <v>11.64</v>
-      </c>
+        <v>11.597</v>
+      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="1">
-        <v>11.48</v>
+        <v>11.132999999999999</v>
       </c>
       <c r="D28" s="1">
-        <v>11.492000000000001</v>
+        <v>11.233000000000001</v>
       </c>
       <c r="E28" s="1">
+        <v>11.285</v>
+      </c>
+      <c r="F28" s="1">
+        <v>11.420999999999999</v>
+      </c>
+      <c r="G28" s="1">
         <v>11.64</v>
-      </c>
-      <c r="F28" s="1">
-        <v>11.801</v>
-      </c>
-      <c r="G28" s="1">
-        <v>11.956</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="1">
-        <v>11.692</v>
+        <v>11.48</v>
       </c>
       <c r="D29" s="1">
-        <v>11.71</v>
+        <v>11.492000000000001</v>
       </c>
       <c r="E29" s="1">
-        <v>11.728</v>
+        <v>11.64</v>
       </c>
       <c r="F29" s="1">
-        <v>11.891999999999999</v>
+        <v>11.801</v>
       </c>
       <c r="G29" s="1">
-        <v>12.129</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="1">
-        <v>11.234999999999999</v>
+        <v>11.692</v>
       </c>
       <c r="D30" s="1">
-        <v>11.53</v>
+        <v>11.71</v>
       </c>
       <c r="E30" s="1">
-        <v>11.542999999999999</v>
+        <v>11.728</v>
       </c>
       <c r="F30" s="1">
-        <v>11.849</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>11.891999999999999</v>
+      </c>
+      <c r="G30" s="1">
+        <v>12.129</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2000</v>
       </c>
       <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1">
+        <v>11.234999999999999</v>
+      </c>
+      <c r="D31" s="1">
+        <v>11.53</v>
+      </c>
+      <c r="E31" s="1">
+        <v>11.542999999999999</v>
+      </c>
+      <c r="F31" s="1">
+        <v>11.849</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>2000</v>
+      </c>
+      <c r="B32" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C32" s="1">
         <v>11.262</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>11.439</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E32" s="1">
         <v>11.494</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F32" s="1">
         <v>11.648999999999999</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Women_F200.xlsx
+++ b/pages/WR_progressions/Medals_Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC67BC5E-73A9-4B2C-93DF-63CFC7EB1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F46A049-3411-44AC-82D3-D0BD334A30B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="9">
   <si>
     <t>8th</t>
   </si>
@@ -101,10 +101,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1400477D-CA59-426F-9BF4-08585135C868}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -476,91 +479,91 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10.029</v>
-      </c>
-      <c r="D2" s="2">
-        <v>10.067</v>
-      </c>
-      <c r="E2" s="2">
-        <v>10.108000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>10.377000000000001</v>
+      </c>
+      <c r="D2">
+        <v>10.382</v>
+      </c>
+      <c r="E2">
+        <v>10.430999999999999</v>
       </c>
       <c r="F2" s="2">
-        <v>10.263</v>
-      </c>
-      <c r="G2" s="2">
-        <v>10.56</v>
+        <v>10.728</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10.9709</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1">
-        <v>10.234</v>
-      </c>
-      <c r="D3" s="1">
-        <v>10.308999999999999</v>
-      </c>
-      <c r="E3" s="1">
-        <v>10.397</v>
-      </c>
-      <c r="F3" s="1">
-        <v>10.612</v>
-      </c>
-      <c r="G3" s="1">
-        <v>10.834</v>
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10.029</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10.067</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10.108000000000001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10.263</v>
+      </c>
+      <c r="G3" s="2">
+        <v>10.56</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>10.356999999999999</v>
+        <v>10.234</v>
       </c>
       <c r="D4" s="1">
-        <v>10.401</v>
+        <v>10.308999999999999</v>
       </c>
       <c r="E4" s="1">
-        <v>10.416</v>
+        <v>10.397</v>
       </c>
       <c r="F4" s="1">
-        <v>10.558999999999999</v>
+        <v>10.612</v>
       </c>
       <c r="G4" s="1">
-        <v>10.734</v>
+        <v>10.834</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>10.489052051920808</v>
+        <v>10.356999999999999</v>
       </c>
       <c r="D5" s="1">
-        <v>10.518934081346424</v>
+        <v>10.401</v>
       </c>
       <c r="E5" s="1">
-        <v>10.520009935564939</v>
+        <v>10.416</v>
       </c>
       <c r="F5" s="1">
-        <v>10.753972995578923</v>
+        <v>10.558999999999999</v>
       </c>
       <c r="G5" s="1">
-        <v>10.952069484796398</v>
+        <v>10.734</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -568,137 +571,137 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
-        <v>10.310016467387413</v>
+        <v>10.489052051920808</v>
       </c>
       <c r="D6" s="1">
-        <v>10.346016783538339</v>
+        <v>10.518934081346424</v>
       </c>
       <c r="E6" s="1">
-        <v>10.381071845668066</v>
+        <v>10.520009935564939</v>
       </c>
       <c r="F6" s="1">
-        <v>10.49501486793773</v>
+        <v>10.753972995578923</v>
       </c>
       <c r="G6" s="1">
-        <v>10.706001308511272</v>
+        <v>10.952069484796398</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
-        <v>10.364036792330612</v>
+        <v>10.310016467387413</v>
       </c>
       <c r="D7" s="1">
-        <v>10.461010940473942</v>
+        <v>10.346016783538339</v>
       </c>
       <c r="E7" s="1">
-        <v>10.478061558611657</v>
+        <v>10.381071845668066</v>
       </c>
       <c r="F7" s="1">
-        <v>10.512944062376802</v>
+        <v>10.49501486793773</v>
       </c>
       <c r="G7" s="1">
-        <v>10.634055562940317</v>
+        <v>10.706001308511272</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1">
-        <v>10.546051089758611</v>
+        <v>10.364036792330612</v>
       </c>
       <c r="D8" s="1">
-        <v>10.661928031985784</v>
+        <v>10.461010940473942</v>
       </c>
       <c r="E8" s="1">
-        <v>10.685029087023626</v>
+        <v>10.478061558611657</v>
       </c>
       <c r="F8" s="1">
-        <v>10.782962918588629</v>
+        <v>10.512944062376802</v>
       </c>
       <c r="G8" s="1">
-        <v>10.971930145378074</v>
+        <v>10.634055562940317</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>10.645</v>
+        <v>10.546051089758611</v>
       </c>
       <c r="D9" s="1">
-        <v>10.712999999999999</v>
+        <v>10.661928031985784</v>
       </c>
       <c r="E9" s="1">
-        <v>10.81</v>
+        <v>10.685029087023626</v>
       </c>
       <c r="F9" s="1">
-        <v>10.975</v>
+        <v>10.782962918588629</v>
       </c>
       <c r="G9" s="1">
-        <v>11.101000000000001</v>
+        <v>10.971930145378074</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>10.724</v>
+        <v>10.645</v>
       </c>
       <c r="D10" s="1">
-        <v>10.763999999999999</v>
+        <v>10.712999999999999</v>
       </c>
       <c r="E10" s="1">
-        <v>10.816000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="F10" s="1">
-        <v>10.967000000000001</v>
+        <v>10.975</v>
       </c>
       <c r="G10" s="1">
-        <v>11.151</v>
+        <v>11.101000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="1">
-        <v>10.76</v>
+        <v>10.724</v>
       </c>
       <c r="D11" s="1">
-        <v>10.779</v>
+        <v>10.763999999999999</v>
       </c>
       <c r="E11" s="1">
-        <v>10.811999999999999</v>
+        <v>10.816000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>10.958</v>
+        <v>10.967000000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>11.106999999999999</v>
+        <v>11.151</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -706,114 +709,114 @@
         <v>2016</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
-        <v>10.721</v>
+        <v>10.76</v>
       </c>
       <c r="D12" s="1">
-        <v>10.787000000000001</v>
+        <v>10.779</v>
       </c>
       <c r="E12" s="1">
-        <v>10.8</v>
+        <v>10.811999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>10.875</v>
+        <v>10.958</v>
       </c>
       <c r="G12" s="1">
-        <v>11.099</v>
+        <v>11.106999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>10.627000000000001</v>
+        <v>10.721</v>
       </c>
       <c r="D13" s="1">
-        <v>10.731999999999999</v>
+        <v>10.787000000000001</v>
       </c>
       <c r="E13" s="1">
-        <v>10.754</v>
+        <v>10.8</v>
       </c>
       <c r="F13" s="1">
-        <v>10.87</v>
+        <v>10.875</v>
       </c>
       <c r="G13" s="1">
-        <v>11.066000000000001</v>
+        <v>11.099</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="1">
-        <v>10.946</v>
+        <v>10.627000000000001</v>
       </c>
       <c r="D14" s="1">
-        <v>10.954000000000001</v>
+        <v>10.731999999999999</v>
       </c>
       <c r="E14" s="1">
-        <v>10.962</v>
+        <v>10.754</v>
       </c>
       <c r="F14" s="1">
-        <v>11.047000000000001</v>
+        <v>10.87</v>
       </c>
       <c r="G14" s="1">
-        <v>11.218</v>
+        <v>11.066000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="1">
-        <v>10.957000000000001</v>
+        <v>10.946</v>
       </c>
       <c r="D15" s="1">
-        <v>11.057</v>
+        <v>10.954000000000001</v>
       </c>
       <c r="E15" s="1">
-        <v>11.07</v>
+        <v>10.962</v>
       </c>
       <c r="F15" s="1">
-        <v>11.208</v>
+        <v>11.047000000000001</v>
       </c>
       <c r="G15" s="1">
-        <v>11.452999999999999</v>
+        <v>11.218</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>10.782</v>
+        <v>10.957000000000001</v>
       </c>
       <c r="D16" s="1">
-        <v>11.004</v>
+        <v>11.057</v>
       </c>
       <c r="E16" s="1">
-        <v>11.032999999999999</v>
+        <v>11.07</v>
       </c>
       <c r="F16" s="1">
-        <v>11.09</v>
+        <v>11.208</v>
       </c>
       <c r="G16" s="1">
-        <v>11.228</v>
+        <v>11.452999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -821,114 +824,114 @@
         <v>2012</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
-        <v>10.724</v>
+        <v>10.782</v>
       </c>
       <c r="D17" s="1">
-        <v>10.805</v>
+        <v>11.004</v>
       </c>
       <c r="E17" s="1">
-        <v>11.02</v>
+        <v>11.032999999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>11.234</v>
+        <v>11.09</v>
       </c>
       <c r="G17" s="1">
-        <v>11.569000000000001</v>
+        <v>11.228</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1">
-        <v>11.12</v>
+        <v>10.724</v>
       </c>
       <c r="D18" s="1">
-        <v>11.12</v>
+        <v>10.805</v>
       </c>
       <c r="E18" s="1">
-        <v>11.151999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="F18" s="1">
-        <v>11.368</v>
+        <v>11.234</v>
       </c>
       <c r="G18" s="1">
-        <v>11.513999999999999</v>
+        <v>11.569000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="1">
-        <v>10.917999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="D19" s="1">
-        <v>11.03</v>
+        <v>11.12</v>
       </c>
       <c r="E19" s="1">
-        <v>11.077</v>
+        <v>11.151999999999999</v>
       </c>
       <c r="F19" s="1">
-        <v>11.202</v>
+        <v>11.368</v>
       </c>
       <c r="G19" s="1">
-        <v>11.442</v>
+        <v>11.513999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="1">
-        <v>10.971</v>
+        <v>10.917999999999999</v>
       </c>
       <c r="D20" s="1">
-        <v>11.134</v>
+        <v>11.03</v>
       </c>
       <c r="E20" s="1">
-        <v>11.148</v>
+        <v>11.077</v>
       </c>
       <c r="F20" s="1">
-        <v>11.430999999999999</v>
+        <v>11.202</v>
       </c>
       <c r="G20" s="1">
-        <v>11.613</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="1">
-        <v>10.904</v>
+        <v>10.971</v>
       </c>
       <c r="D21" s="1">
-        <v>11.002000000000001</v>
+        <v>11.134</v>
       </c>
       <c r="E21" s="1">
-        <v>11.093</v>
+        <v>11.148</v>
       </c>
       <c r="F21" s="1">
-        <v>11.28</v>
+        <v>11.430999999999999</v>
       </c>
       <c r="G21" s="1">
-        <v>11.417</v>
+        <v>11.613</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -936,110 +939,110 @@
         <v>2008</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>10.962999999999999</v>
+        <v>10.904</v>
       </c>
       <c r="D22" s="1">
-        <v>11.106</v>
+        <v>11.002000000000001</v>
       </c>
       <c r="E22" s="1">
-        <v>11.14</v>
+        <v>11.093</v>
       </c>
       <c r="F22" s="1">
-        <v>11.4</v>
-      </c>
-      <c r="G22" s="1"/>
+        <v>11.28</v>
+      </c>
+      <c r="G22" s="1">
+        <v>11.417</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1">
-        <v>11.148999999999999</v>
+        <v>10.962999999999999</v>
       </c>
       <c r="D23" s="1">
-        <v>11.191000000000001</v>
+        <v>11.106</v>
       </c>
       <c r="E23" s="1">
-        <v>11.194000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F23" s="1">
-        <v>11.407999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="1">
-        <v>11.052</v>
+        <v>11.148999999999999</v>
       </c>
       <c r="D24" s="1">
-        <v>11.268000000000001</v>
+        <v>11.191000000000001</v>
       </c>
       <c r="E24" s="1">
-        <v>11.365</v>
+        <v>11.194000000000001</v>
       </c>
       <c r="F24" s="1">
-        <v>11.507</v>
-      </c>
-      <c r="G24" s="1">
-        <v>11.755000000000001</v>
-      </c>
+        <v>11.407999999999999</v>
+      </c>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1">
-        <v>11.278</v>
+        <v>11.052</v>
       </c>
       <c r="D25" s="1">
-        <v>11.385999999999999</v>
+        <v>11.268000000000001</v>
       </c>
       <c r="E25" s="1">
-        <v>11.494</v>
+        <v>11.365</v>
       </c>
       <c r="F25" s="1">
-        <v>11.65</v>
+        <v>11.507</v>
       </c>
       <c r="G25" s="1">
-        <v>11.933</v>
+        <v>11.755000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="1">
-        <v>11.339</v>
+        <v>11.278</v>
       </c>
       <c r="D26" s="1">
-        <v>11.45</v>
+        <v>11.385999999999999</v>
       </c>
       <c r="E26" s="1">
-        <v>11.452</v>
+        <v>11.494</v>
       </c>
       <c r="F26" s="1">
-        <v>11.558999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="G26" s="1">
-        <v>11.84</v>
+        <v>11.933</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -1047,132 +1050,155 @@
         <v>2004</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1">
-        <v>11.291</v>
+        <v>11.339</v>
       </c>
       <c r="D27" s="1">
-        <v>11.364000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="E27" s="1">
-        <v>11.364000000000001</v>
+        <v>11.452</v>
       </c>
       <c r="F27" s="1">
-        <v>11.597</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>11.558999999999999</v>
+      </c>
+      <c r="G27" s="1">
+        <v>11.84</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1">
-        <v>11.132999999999999</v>
+        <v>11.291</v>
       </c>
       <c r="D28" s="1">
-        <v>11.233000000000001</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="E28" s="1">
-        <v>11.285</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="F28" s="1">
-        <v>11.420999999999999</v>
-      </c>
-      <c r="G28" s="1">
-        <v>11.64</v>
-      </c>
+        <v>11.597</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="1">
-        <v>11.48</v>
+        <v>11.132999999999999</v>
       </c>
       <c r="D29" s="1">
-        <v>11.492000000000001</v>
+        <v>11.233000000000001</v>
       </c>
       <c r="E29" s="1">
+        <v>11.285</v>
+      </c>
+      <c r="F29" s="1">
+        <v>11.420999999999999</v>
+      </c>
+      <c r="G29" s="1">
         <v>11.64</v>
-      </c>
-      <c r="F29" s="1">
-        <v>11.801</v>
-      </c>
-      <c r="G29" s="1">
-        <v>11.956</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="1">
-        <v>11.692</v>
+        <v>11.48</v>
       </c>
       <c r="D30" s="1">
-        <v>11.71</v>
+        <v>11.492000000000001</v>
       </c>
       <c r="E30" s="1">
-        <v>11.728</v>
+        <v>11.64</v>
       </c>
       <c r="F30" s="1">
-        <v>11.891999999999999</v>
+        <v>11.801</v>
       </c>
       <c r="G30" s="1">
-        <v>12.129</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="1">
-        <v>11.234999999999999</v>
+        <v>11.692</v>
       </c>
       <c r="D31" s="1">
-        <v>11.53</v>
+        <v>11.71</v>
       </c>
       <c r="E31" s="1">
-        <v>11.542999999999999</v>
+        <v>11.728</v>
       </c>
       <c r="F31" s="1">
-        <v>11.849</v>
-      </c>
-      <c r="G31" s="1"/>
+        <v>11.891999999999999</v>
+      </c>
+      <c r="G31" s="1">
+        <v>12.129</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>2000</v>
       </c>
       <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1">
+        <v>11.234999999999999</v>
+      </c>
+      <c r="D32" s="1">
+        <v>11.53</v>
+      </c>
+      <c r="E32" s="1">
+        <v>11.542999999999999</v>
+      </c>
+      <c r="F32" s="1">
+        <v>11.849</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>2000</v>
+      </c>
+      <c r="B33" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C33" s="1">
         <v>11.262</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>11.439</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E33" s="1">
         <v>11.494</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F33" s="1">
         <v>11.648999999999999</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Women_F200.xlsx
+++ b/pages/WR_progressions/Medals_Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F46A049-3411-44AC-82D3-D0BD334A30B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A90394F-D887-4BF3-89C9-69AF19F27D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>

--- a/pages/WR_progressions/Medals_Women_F200.xlsx
+++ b/pages/WR_progressions/Medals_Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A90394F-D887-4BF3-89C9-69AF19F27D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6914EA47-2203-417F-810F-909EA911A005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
   <si>
     <t>8th</t>
   </si>
@@ -444,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1400477D-CA59-426F-9BF4-08585135C868}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="9.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -474,372 +474,377 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>10.377000000000001</v>
-      </c>
-      <c r="D2">
-        <v>10.382</v>
-      </c>
-      <c r="E2">
-        <v>10.430999999999999</v>
+      <c r="C2" s="2">
+        <v>10.331</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10.339</v>
+      </c>
+      <c r="E2" s="2">
+        <v>10.340999999999999</v>
       </c>
       <c r="F2" s="2">
-        <v>10.728</v>
-      </c>
-      <c r="G2" s="3">
-        <v>10.9709</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+        <v>10.452999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>10.739000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2024</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>10.377000000000001</v>
+      </c>
+      <c r="D3">
+        <v>10.382</v>
+      </c>
+      <c r="E3">
+        <v>10.430999999999999</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10.728</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.9709</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C4" s="2">
         <v>10.029</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>10.067</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E4" s="2">
         <v>10.108000000000001</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F4" s="2">
         <v>10.263</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G4" s="2">
         <v>10.56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5">
         <v>2023</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1">
         <v>10.234</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D5" s="1">
         <v>10.308999999999999</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E5" s="1">
         <v>10.397</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F5" s="1">
         <v>10.612</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G5" s="1">
         <v>10.834</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6">
         <v>2022</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
         <v>10.356999999999999</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D6" s="1">
         <v>10.401</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E6" s="1">
         <v>10.416</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F6" s="1">
         <v>10.558999999999999</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G6" s="1">
         <v>10.734</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10.489052051920808</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10.518934081346424</v>
-      </c>
-      <c r="E6" s="1">
-        <v>10.520009935564939</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10.753972995578923</v>
-      </c>
-      <c r="G6" s="1">
-        <v>10.952069484796398</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2021</v>
       </c>
       <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10.489052051920808</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10.518934081346424</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10.520009935564939</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10.753972995578923</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10.952069484796398</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="1">
         <v>10.310016467387413</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D8" s="1">
         <v>10.346016783538339</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <v>10.381071845668066</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <v>10.49501486793773</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" s="1">
         <v>10.706001308511272</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9">
         <v>2020</v>
       </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
         <v>10.364036792330612</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>10.461010940473942</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9" s="1">
         <v>10.478061558611657</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F9" s="1">
         <v>10.512944062376802</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" s="1">
         <v>10.634055562940317</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2019</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
         <v>10.546051089758611</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
         <v>10.661928031985784</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E10" s="1">
         <v>10.685029087023626</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F10" s="1">
         <v>10.782962918588629</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" s="1">
         <v>10.971930145378074</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11">
         <v>2018</v>
       </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
         <v>10.645</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>10.712999999999999</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>10.81</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>10.975</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>11.101000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12">
         <v>2017</v>
       </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
         <v>10.724</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>10.763999999999999</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E12" s="1">
         <v>10.816000000000001</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="1">
         <v>10.967000000000001</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="1">
         <v>11.151</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>2016</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1">
-        <v>10.76</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10.779</v>
-      </c>
-      <c r="E12" s="1">
-        <v>10.811999999999999</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10.958</v>
-      </c>
-      <c r="G12" s="1">
-        <v>11.106999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2016</v>
       </c>
       <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10.76</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10.779</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10.811999999999999</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10.958</v>
+      </c>
+      <c r="G13" s="1">
+        <v>11.106999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2016</v>
+      </c>
+      <c r="B14" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C14" s="1">
         <v>10.721</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>10.787000000000001</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E14" s="1">
         <v>10.8</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>10.875</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <v>11.099</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>2015</v>
       </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1">
         <v>10.627000000000001</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15" s="1">
         <v>10.731999999999999</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E15" s="1">
         <v>10.754</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>10.87</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <v>11.066000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16">
         <v>2014</v>
       </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1">
         <v>10.946</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>10.954000000000001</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E16" s="1">
         <v>10.962</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>11.047000000000001</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" s="1">
         <v>11.218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>2013</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10.957000000000001</v>
-      </c>
-      <c r="D16" s="1">
-        <v>11.057</v>
-      </c>
-      <c r="E16" s="1">
-        <v>11.07</v>
-      </c>
-      <c r="F16" s="1">
-        <v>11.208</v>
-      </c>
-      <c r="G16" s="1">
-        <v>11.452999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="1">
-        <v>10.782</v>
+        <v>10.957000000000001</v>
       </c>
       <c r="D17" s="1">
-        <v>11.004</v>
+        <v>11.057</v>
       </c>
       <c r="E17" s="1">
-        <v>11.032999999999999</v>
+        <v>11.07</v>
       </c>
       <c r="F17" s="1">
-        <v>11.09</v>
+        <v>11.208</v>
       </c>
       <c r="G17" s="1">
-        <v>11.228</v>
+        <v>11.452999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -847,114 +852,114 @@
         <v>2012</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1">
-        <v>10.724</v>
+        <v>10.782</v>
       </c>
       <c r="D18" s="1">
-        <v>10.805</v>
+        <v>11.004</v>
       </c>
       <c r="E18" s="1">
-        <v>11.02</v>
+        <v>11.032999999999999</v>
       </c>
       <c r="F18" s="1">
-        <v>11.234</v>
+        <v>11.09</v>
       </c>
       <c r="G18" s="1">
-        <v>11.569000000000001</v>
+        <v>11.228</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>11.12</v>
+        <v>10.724</v>
       </c>
       <c r="D19" s="1">
-        <v>11.12</v>
+        <v>10.805</v>
       </c>
       <c r="E19" s="1">
-        <v>11.151999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="F19" s="1">
-        <v>11.368</v>
+        <v>11.234</v>
       </c>
       <c r="G19" s="1">
-        <v>11.513999999999999</v>
+        <v>11.569000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="1">
-        <v>10.917999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="D20" s="1">
-        <v>11.03</v>
+        <v>11.12</v>
       </c>
       <c r="E20" s="1">
-        <v>11.077</v>
+        <v>11.151999999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>11.202</v>
+        <v>11.368</v>
       </c>
       <c r="G20" s="1">
-        <v>11.442</v>
+        <v>11.513999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="1">
-        <v>10.971</v>
+        <v>10.917999999999999</v>
       </c>
       <c r="D21" s="1">
-        <v>11.134</v>
+        <v>11.03</v>
       </c>
       <c r="E21" s="1">
-        <v>11.148</v>
+        <v>11.077</v>
       </c>
       <c r="F21" s="1">
-        <v>11.430999999999999</v>
+        <v>11.202</v>
       </c>
       <c r="G21" s="1">
-        <v>11.613</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>10.904</v>
+        <v>10.971</v>
       </c>
       <c r="D22" s="1">
-        <v>11.002000000000001</v>
+        <v>11.134</v>
       </c>
       <c r="E22" s="1">
-        <v>11.093</v>
+        <v>11.148</v>
       </c>
       <c r="F22" s="1">
-        <v>11.28</v>
+        <v>11.430999999999999</v>
       </c>
       <c r="G22" s="1">
-        <v>11.417</v>
+        <v>11.613</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -962,110 +967,110 @@
         <v>2008</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1">
-        <v>10.962999999999999</v>
+        <v>10.904</v>
       </c>
       <c r="D23" s="1">
-        <v>11.106</v>
+        <v>11.002000000000001</v>
       </c>
       <c r="E23" s="1">
-        <v>11.14</v>
+        <v>11.093</v>
       </c>
       <c r="F23" s="1">
-        <v>11.4</v>
-      </c>
-      <c r="G23" s="1"/>
+        <v>11.28</v>
+      </c>
+      <c r="G23" s="1">
+        <v>11.417</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1">
-        <v>11.148999999999999</v>
+        <v>10.962999999999999</v>
       </c>
       <c r="D24" s="1">
-        <v>11.191000000000001</v>
+        <v>11.106</v>
       </c>
       <c r="E24" s="1">
-        <v>11.194000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F24" s="1">
-        <v>11.407999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1">
-        <v>11.052</v>
+        <v>11.148999999999999</v>
       </c>
       <c r="D25" s="1">
-        <v>11.268000000000001</v>
+        <v>11.191000000000001</v>
       </c>
       <c r="E25" s="1">
-        <v>11.365</v>
+        <v>11.194000000000001</v>
       </c>
       <c r="F25" s="1">
-        <v>11.507</v>
-      </c>
-      <c r="G25" s="1">
-        <v>11.755000000000001</v>
-      </c>
+        <v>11.407999999999999</v>
+      </c>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="1">
-        <v>11.278</v>
+        <v>11.052</v>
       </c>
       <c r="D26" s="1">
-        <v>11.385999999999999</v>
+        <v>11.268000000000001</v>
       </c>
       <c r="E26" s="1">
-        <v>11.494</v>
+        <v>11.365</v>
       </c>
       <c r="F26" s="1">
-        <v>11.65</v>
+        <v>11.507</v>
       </c>
       <c r="G26" s="1">
-        <v>11.933</v>
+        <v>11.755000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="1">
-        <v>11.339</v>
+        <v>11.278</v>
       </c>
       <c r="D27" s="1">
-        <v>11.45</v>
+        <v>11.385999999999999</v>
       </c>
       <c r="E27" s="1">
-        <v>11.452</v>
+        <v>11.494</v>
       </c>
       <c r="F27" s="1">
-        <v>11.558999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="G27" s="1">
-        <v>11.84</v>
+        <v>11.933</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -1073,132 +1078,155 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="1">
-        <v>11.291</v>
+        <v>11.339</v>
       </c>
       <c r="D28" s="1">
-        <v>11.364000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="E28" s="1">
-        <v>11.364000000000001</v>
+        <v>11.452</v>
       </c>
       <c r="F28" s="1">
-        <v>11.597</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>11.558999999999999</v>
+      </c>
+      <c r="G28" s="1">
+        <v>11.84</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1">
-        <v>11.132999999999999</v>
+        <v>11.291</v>
       </c>
       <c r="D29" s="1">
-        <v>11.233000000000001</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="E29" s="1">
-        <v>11.285</v>
+        <v>11.364000000000001</v>
       </c>
       <c r="F29" s="1">
-        <v>11.420999999999999</v>
-      </c>
-      <c r="G29" s="1">
-        <v>11.64</v>
-      </c>
+        <v>11.597</v>
+      </c>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="1">
-        <v>11.48</v>
+        <v>11.132999999999999</v>
       </c>
       <c r="D30" s="1">
-        <v>11.492000000000001</v>
+        <v>11.233000000000001</v>
       </c>
       <c r="E30" s="1">
+        <v>11.285</v>
+      </c>
+      <c r="F30" s="1">
+        <v>11.420999999999999</v>
+      </c>
+      <c r="G30" s="1">
         <v>11.64</v>
-      </c>
-      <c r="F30" s="1">
-        <v>11.801</v>
-      </c>
-      <c r="G30" s="1">
-        <v>11.956</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="1">
-        <v>11.692</v>
+        <v>11.48</v>
       </c>
       <c r="D31" s="1">
-        <v>11.71</v>
+        <v>11.492000000000001</v>
       </c>
       <c r="E31" s="1">
-        <v>11.728</v>
+        <v>11.64</v>
       </c>
       <c r="F31" s="1">
-        <v>11.891999999999999</v>
+        <v>11.801</v>
       </c>
       <c r="G31" s="1">
-        <v>12.129</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>11.234999999999999</v>
+        <v>11.692</v>
       </c>
       <c r="D32" s="1">
-        <v>11.53</v>
+        <v>11.71</v>
       </c>
       <c r="E32" s="1">
-        <v>11.542999999999999</v>
+        <v>11.728</v>
       </c>
       <c r="F32" s="1">
-        <v>11.849</v>
-      </c>
-      <c r="G32" s="1"/>
+        <v>11.891999999999999</v>
+      </c>
+      <c r="G32" s="1">
+        <v>12.129</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>2000</v>
       </c>
       <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1">
+        <v>11.234999999999999</v>
+      </c>
+      <c r="D33" s="1">
+        <v>11.53</v>
+      </c>
+      <c r="E33" s="1">
+        <v>11.542999999999999</v>
+      </c>
+      <c r="F33" s="1">
+        <v>11.849</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>2000</v>
+      </c>
+      <c r="B34" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C34" s="1">
         <v>11.262</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>11.439</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34" s="1">
         <v>11.494</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34" s="1">
         <v>11.648999999999999</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
